--- a/data/nzd0290/nzd0290.xlsx
+++ b/data/nzd0290/nzd0290.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H816"/>
+  <dimension ref="A1:H818"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24918,6 +24918,66 @@
         <v>367.82</v>
       </c>
       <c r="H816" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B817" t="n">
+        <v>373.28</v>
+      </c>
+      <c r="C817" t="n">
+        <v>387.86</v>
+      </c>
+      <c r="D817" t="n">
+        <v>387.74</v>
+      </c>
+      <c r="E817" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="F817" t="n">
+        <v>384.68</v>
+      </c>
+      <c r="G817" t="n">
+        <v>367.4</v>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:54:26+00:00</t>
+        </is>
+      </c>
+      <c r="B818" t="n">
+        <v>374.18</v>
+      </c>
+      <c r="C818" t="n">
+        <v>387.66</v>
+      </c>
+      <c r="D818" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="E818" t="n">
+        <v>386.71</v>
+      </c>
+      <c r="F818" t="n">
+        <v>386.02</v>
+      </c>
+      <c r="G818" t="n">
+        <v>368.53</v>
+      </c>
+      <c r="H818" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24934,7 +24994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B827"/>
+  <dimension ref="A1:B829"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33207,6 +33267,26 @@
       </c>
       <c r="B827" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B828" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B829" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -33375,28 +33455,28 @@
         <v>0.0479</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2977107971464694</v>
+        <v>-0.2989059032104056</v>
       </c>
       <c r="J2" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="K2" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1223947570699914</v>
+        <v>0.123825792250979</v>
       </c>
       <c r="M2" t="n">
-        <v>4.546114615186759</v>
+        <v>4.541078384532858</v>
       </c>
       <c r="N2" t="n">
-        <v>34.61122886698654</v>
+        <v>34.54078052689083</v>
       </c>
       <c r="O2" t="n">
-        <v>5.883130872841988</v>
+        <v>5.877140505968088</v>
       </c>
       <c r="P2" t="n">
-        <v>383.9396790379486</v>
+        <v>383.9518698864613</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33453,28 +33533,28 @@
         <v>0.0776</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2485931825256995</v>
+        <v>-0.2501936264878619</v>
       </c>
       <c r="J3" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="K3" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1434146539112318</v>
+        <v>0.1455482470207488</v>
       </c>
       <c r="M3" t="n">
-        <v>3.513131266282062</v>
+        <v>3.512217560787787</v>
       </c>
       <c r="N3" t="n">
-        <v>20.10235755345149</v>
+        <v>20.07783421293384</v>
       </c>
       <c r="O3" t="n">
-        <v>4.483565272576222</v>
+        <v>4.480829634446487</v>
       </c>
       <c r="P3" t="n">
-        <v>397.4786569483774</v>
+        <v>397.4949860876546</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33531,28 +33611,28 @@
         <v>0.0718</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1797337981580046</v>
+        <v>-0.181638834233587</v>
       </c>
       <c r="J4" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="K4" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1283193621074253</v>
+        <v>0.1310061180313087</v>
       </c>
       <c r="M4" t="n">
-        <v>2.884328227991977</v>
+        <v>2.887477554347394</v>
       </c>
       <c r="N4" t="n">
-        <v>11.95132797822089</v>
+        <v>11.95711390745535</v>
       </c>
       <c r="O4" t="n">
-        <v>3.457069275878181</v>
+        <v>3.457906000378748</v>
       </c>
       <c r="P4" t="n">
-        <v>396.4408410730401</v>
+        <v>396.4602764340764</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33609,28 +33689,28 @@
         <v>0.0693</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06596359666947621</v>
+        <v>-0.06764274742384495</v>
       </c>
       <c r="J5" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="K5" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02421368295494708</v>
+        <v>0.02549995442342645</v>
       </c>
       <c r="M5" t="n">
-        <v>2.498015954793862</v>
+        <v>2.499471974795946</v>
       </c>
       <c r="N5" t="n">
-        <v>9.549793504673321</v>
+        <v>9.553637333156324</v>
       </c>
       <c r="O5" t="n">
-        <v>3.090274017732622</v>
+        <v>3.090895878731007</v>
       </c>
       <c r="P5" t="n">
-        <v>391.6363014641523</v>
+        <v>391.6534323432404</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33687,28 +33767,28 @@
         <v>0.0736</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02053261180903494</v>
+        <v>-0.02299588228513797</v>
       </c>
       <c r="J6" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="K6" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001170076414740207</v>
+        <v>0.001471060563061233</v>
       </c>
       <c r="M6" t="n">
-        <v>3.662226500725118</v>
+        <v>3.665559930125711</v>
       </c>
       <c r="N6" t="n">
-        <v>19.60004939161436</v>
+        <v>19.61164713803815</v>
       </c>
       <c r="O6" t="n">
-        <v>4.427194302446456</v>
+        <v>4.42850393903383</v>
       </c>
       <c r="P6" t="n">
-        <v>390.7965004428711</v>
+        <v>390.821628757659</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33765,28 +33845,28 @@
         <v>0.0537</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03662242083760282</v>
+        <v>-0.03992389136600129</v>
       </c>
       <c r="J7" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="K7" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003321117617865244</v>
+        <v>0.003947694012889413</v>
       </c>
       <c r="M7" t="n">
-        <v>3.820096841560032</v>
+        <v>3.825754135295837</v>
       </c>
       <c r="N7" t="n">
-        <v>21.92080765773595</v>
+        <v>21.97294184477209</v>
       </c>
       <c r="O7" t="n">
-        <v>4.681966217064787</v>
+        <v>4.687530463343369</v>
       </c>
       <c r="P7" t="n">
-        <v>375.5006292169564</v>
+        <v>375.5343098839332</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33824,7 +33904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H816"/>
+  <dimension ref="A1:H818"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68099,6 +68179,90 @@
         </is>
       </c>
     </row>
+    <row r="817">
+      <c r="A817" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>-39.30027633256495,176.97760535763655</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>-39.30078567905948,176.97703637090018</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>-39.301280811184064,176.97648004365408</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>-39.30181407126508,176.97592624693485</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>-39.30234021636327,176.97539732128692</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>-39.30287910312912,176.97484255479637</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-02 21:54:26+00:00</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>-39.30028253648035,176.97761205657923</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>-39.30078441734708,176.97703471935716</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>-39.30128278343427,176.97648335094496</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>-39.301815681313336,176.9759291786154</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>-39.30234608784171,176.975410875687</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>-39.30288319838857,176.97485453317785</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0290/nzd0290.xlsx
+++ b/data/nzd0290/nzd0290.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H818"/>
+  <dimension ref="A1:H819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24978,6 +24978,36 @@
         <v>368.53</v>
       </c>
       <c r="H818" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:33+00:00</t>
+        </is>
+      </c>
+      <c r="B819" t="n">
+        <v>375.17</v>
+      </c>
+      <c r="C819" t="n">
+        <v>389.34</v>
+      </c>
+      <c r="D819" t="n">
+        <v>390.47</v>
+      </c>
+      <c r="E819" t="n">
+        <v>390.1</v>
+      </c>
+      <c r="F819" t="n">
+        <v>388.21</v>
+      </c>
+      <c r="G819" t="n">
+        <v>370.63</v>
+      </c>
+      <c r="H819" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24994,7 +25024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B829"/>
+  <dimension ref="A1:B830"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33287,6 +33317,16 @@
       </c>
       <c r="B829" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B830" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -33455,28 +33495,28 @@
         <v>0.0479</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2989059032104056</v>
+        <v>-0.2991298593146654</v>
       </c>
       <c r="J2" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K2" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="L2" t="n">
-        <v>0.123825792250979</v>
+        <v>0.1242976290389519</v>
       </c>
       <c r="M2" t="n">
-        <v>4.541078384532858</v>
+        <v>4.536653603289031</v>
       </c>
       <c r="N2" t="n">
-        <v>34.54078052689083</v>
+        <v>34.49950912664928</v>
       </c>
       <c r="O2" t="n">
-        <v>5.877140505968088</v>
+        <v>5.873628276172171</v>
       </c>
       <c r="P2" t="n">
-        <v>383.9518698864613</v>
+        <v>383.9541673430672</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33533,28 +33573,28 @@
         <v>0.0776</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2501936264878619</v>
+        <v>-0.2505856297464947</v>
       </c>
       <c r="J3" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K3" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1455482470207488</v>
+        <v>0.1462781554107921</v>
       </c>
       <c r="M3" t="n">
-        <v>3.512217560787787</v>
+        <v>3.509782867556948</v>
       </c>
       <c r="N3" t="n">
-        <v>20.07783421293384</v>
+        <v>20.05621351221271</v>
       </c>
       <c r="O3" t="n">
-        <v>4.480829634446487</v>
+        <v>4.478416406746106</v>
       </c>
       <c r="P3" t="n">
-        <v>397.4949860876546</v>
+        <v>397.4990074581775</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33611,28 +33651,28 @@
         <v>0.0718</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.181638834233587</v>
+        <v>-0.1819392666969916</v>
       </c>
       <c r="J4" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K4" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1310061180313087</v>
+        <v>0.131694478049408</v>
       </c>
       <c r="M4" t="n">
-        <v>2.887477554347394</v>
+        <v>2.885538932179228</v>
       </c>
       <c r="N4" t="n">
-        <v>11.95711390745535</v>
+        <v>11.94421408213601</v>
       </c>
       <c r="O4" t="n">
-        <v>3.457906000378748</v>
+        <v>3.456040231556341</v>
       </c>
       <c r="P4" t="n">
-        <v>396.4602764340764</v>
+        <v>396.4633584244065</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33689,28 +33729,28 @@
         <v>0.0693</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06764274742384495</v>
+        <v>-0.06758464804353786</v>
       </c>
       <c r="J5" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K5" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02549995442342645</v>
+        <v>0.02552845597969355</v>
       </c>
       <c r="M5" t="n">
-        <v>2.499471974795946</v>
+        <v>2.49671558033255</v>
       </c>
       <c r="N5" t="n">
-        <v>9.553637333156324</v>
+        <v>9.542022307594548</v>
       </c>
       <c r="O5" t="n">
-        <v>3.090895878731007</v>
+        <v>3.089016398077962</v>
       </c>
       <c r="P5" t="n">
-        <v>391.6534323432404</v>
+        <v>391.6528363299923</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33767,28 +33807,28 @@
         <v>0.0736</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02299588228513797</v>
+        <v>-0.02350212624987676</v>
       </c>
       <c r="J6" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K6" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001471060563061233</v>
+        <v>0.001540471017378309</v>
       </c>
       <c r="M6" t="n">
-        <v>3.665559930125711</v>
+        <v>3.663581410345584</v>
       </c>
       <c r="N6" t="n">
-        <v>19.61164713803815</v>
+        <v>19.59254917449106</v>
       </c>
       <c r="O6" t="n">
-        <v>4.42850393903383</v>
+        <v>4.426347159282816</v>
       </c>
       <c r="P6" t="n">
-        <v>390.821628757659</v>
+        <v>390.82682206795</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33845,28 +33885,28 @@
         <v>0.0537</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03992389136600129</v>
+        <v>-0.04089762657828969</v>
       </c>
       <c r="J7" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K7" t="n">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003947694012889413</v>
+        <v>0.004150265109782336</v>
       </c>
       <c r="M7" t="n">
-        <v>3.825754135295837</v>
+        <v>3.825442074211986</v>
       </c>
       <c r="N7" t="n">
-        <v>21.97294184477209</v>
+        <v>21.96412388279398</v>
       </c>
       <c r="O7" t="n">
-        <v>4.687530463343369</v>
+        <v>4.686589792460397</v>
       </c>
       <c r="P7" t="n">
-        <v>375.5343098839332</v>
+        <v>375.5442989592624</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33904,7 +33944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H818"/>
+  <dimension ref="A1:H819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68263,6 +68303,48 @@
         </is>
       </c>
     </row>
+    <row r="819">
+      <c r="A819" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:33+00:00</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>-39.30028936078679,176.97761942541754</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>-39.30079501573039,176.9770485923204</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>-39.3012957674121,176.97650512394796</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>-39.30183328796478,176.97596123796927</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>-39.30235568376177,176.97543302803214</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>-39.302890809044236,176.97487679389033</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0290/nzd0290.xlsx
+++ b/data/nzd0290/nzd0290.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H819"/>
+  <dimension ref="A1:H821"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25008,6 +25008,66 @@
         <v>370.63</v>
       </c>
       <c r="H819" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:54:19+00:00</t>
+        </is>
+      </c>
+      <c r="B820" t="n">
+        <v>378.34</v>
+      </c>
+      <c r="C820" t="n">
+        <v>389.94</v>
+      </c>
+      <c r="D820" t="n">
+        <v>391.23</v>
+      </c>
+      <c r="E820" t="n">
+        <v>390.74</v>
+      </c>
+      <c r="F820" t="n">
+        <v>388.18</v>
+      </c>
+      <c r="G820" t="n">
+        <v>371.02</v>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B821" t="n">
+        <v>378.06</v>
+      </c>
+      <c r="C821" t="n">
+        <v>389.59</v>
+      </c>
+      <c r="D821" t="n">
+        <v>390.78</v>
+      </c>
+      <c r="E821" t="n">
+        <v>390.6</v>
+      </c>
+      <c r="F821" t="n">
+        <v>387.72</v>
+      </c>
+      <c r="G821" t="n">
+        <v>371.87</v>
+      </c>
+      <c r="H821" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25024,7 +25084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B830"/>
+  <dimension ref="A1:B832"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33327,6 +33387,26 @@
       </c>
       <c r="B830" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B831" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B832" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -33495,28 +33575,28 @@
         <v>0.0479</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2991298593146654</v>
+        <v>-0.2980296431200929</v>
       </c>
       <c r="J2" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="K2" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1242976290389519</v>
+        <v>0.1240893570689021</v>
       </c>
       <c r="M2" t="n">
-        <v>4.536653603289031</v>
+        <v>4.530637300671871</v>
       </c>
       <c r="N2" t="n">
-        <v>34.49950912664928</v>
+        <v>34.42685936197478</v>
       </c>
       <c r="O2" t="n">
-        <v>5.873628276172171</v>
+        <v>5.867440614269119</v>
       </c>
       <c r="P2" t="n">
-        <v>383.9541673430672</v>
+        <v>383.9428392955392</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33573,28 +33653,28 @@
         <v>0.0776</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2505856297464947</v>
+        <v>-0.251136474213718</v>
       </c>
       <c r="J3" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="K3" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1462781554107921</v>
+        <v>0.1475356160831155</v>
       </c>
       <c r="M3" t="n">
-        <v>3.509782867556948</v>
+        <v>3.503806894690102</v>
       </c>
       <c r="N3" t="n">
-        <v>20.05621351221271</v>
+        <v>20.01023389650112</v>
       </c>
       <c r="O3" t="n">
-        <v>4.478416406746106</v>
+        <v>4.473279993081264</v>
       </c>
       <c r="P3" t="n">
-        <v>397.4990074581775</v>
+        <v>397.5046801723875</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33651,28 +33731,28 @@
         <v>0.0718</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1819392666969916</v>
+        <v>-0.182262151885162</v>
       </c>
       <c r="J4" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="K4" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="L4" t="n">
-        <v>0.131694478049408</v>
+        <v>0.1327549813408605</v>
       </c>
       <c r="M4" t="n">
-        <v>2.885538932179228</v>
+        <v>2.880193772074448</v>
       </c>
       <c r="N4" t="n">
-        <v>11.94421408213601</v>
+        <v>11.91618359608727</v>
       </c>
       <c r="O4" t="n">
-        <v>3.456040231556341</v>
+        <v>3.451982560223512</v>
       </c>
       <c r="P4" t="n">
-        <v>396.4633584244065</v>
+        <v>396.4666841274685</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33729,28 +33809,28 @@
         <v>0.0693</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06758464804353786</v>
+        <v>-0.0671770047040945</v>
       </c>
       <c r="J5" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="K5" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02552845597969355</v>
+        <v>0.025367816189107</v>
       </c>
       <c r="M5" t="n">
-        <v>2.49671558033255</v>
+        <v>2.492707182237735</v>
       </c>
       <c r="N5" t="n">
-        <v>9.542022307594548</v>
+        <v>9.520333195298015</v>
       </c>
       <c r="O5" t="n">
-        <v>3.089016398077962</v>
+        <v>3.085503718244075</v>
       </c>
       <c r="P5" t="n">
-        <v>391.6528363299923</v>
+        <v>391.648639246808</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33807,28 +33887,28 @@
         <v>0.0736</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02350212624987676</v>
+        <v>-0.02464437028592497</v>
       </c>
       <c r="J6" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="K6" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001540471017378309</v>
+        <v>0.001702320994652062</v>
       </c>
       <c r="M6" t="n">
-        <v>3.663581410345584</v>
+        <v>3.660233621667925</v>
       </c>
       <c r="N6" t="n">
-        <v>19.59254917449106</v>
+        <v>19.55722661487264</v>
       </c>
       <c r="O6" t="n">
-        <v>4.426347159282816</v>
+        <v>4.422355324357444</v>
       </c>
       <c r="P6" t="n">
-        <v>390.82682206795</v>
+        <v>390.8385845733497</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33885,28 +33965,28 @@
         <v>0.0537</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04089762657828969</v>
+        <v>-0.0424219951817704</v>
       </c>
       <c r="J7" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="K7" t="n">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004150265109782336</v>
+        <v>0.004485234698441976</v>
       </c>
       <c r="M7" t="n">
-        <v>3.825442074211986</v>
+        <v>3.822883811487078</v>
       </c>
       <c r="N7" t="n">
-        <v>21.96412388279398</v>
+        <v>21.93299421550751</v>
       </c>
       <c r="O7" t="n">
-        <v>4.686589792460397</v>
+        <v>4.683267472129636</v>
       </c>
       <c r="P7" t="n">
-        <v>375.5442989592624</v>
+        <v>375.5599930181323</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33944,7 +34024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H819"/>
+  <dimension ref="A1:H821"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68345,6 +68425,90 @@
         </is>
       </c>
     </row>
+    <row r="820">
+      <c r="A820" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:54:19+00:00</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>-39.300311212350174,176.9776430205965</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>-39.30079880086684,176.9770535469511</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>-39.30129993104961,176.97651210600966</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>-39.30183661193328,176.97596729047441</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>-39.30235555231084,176.97543272457534</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>-39.30289222245123,176.97488092802314</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>-39.30030928224385,176.97764093647916</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>-39.30079659287061,176.97705065674978</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>-39.30129746573799,176.97650797189408</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>-39.301835884815205,176.97596596648887</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>-39.30235353672982,176.97542807157086</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>-39.302895302953075,176.97488993831317</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0290/nzd0290.xlsx
+++ b/data/nzd0290/nzd0290.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H821"/>
+  <dimension ref="A1:H825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25068,6 +25068,126 @@
         <v>371.87</v>
       </c>
       <c r="H821" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="B822" t="n">
+        <v>378.15</v>
+      </c>
+      <c r="C822" t="n">
+        <v>390.25</v>
+      </c>
+      <c r="D822" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="E822" t="n">
+        <v>390.98</v>
+      </c>
+      <c r="F822" t="n">
+        <v>388.26</v>
+      </c>
+      <c r="G822" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="B823" t="n">
+        <v>380.14</v>
+      </c>
+      <c r="C823" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="D823" t="n">
+        <v>391.84</v>
+      </c>
+      <c r="E823" t="n">
+        <v>391.04</v>
+      </c>
+      <c r="F823" t="n">
+        <v>388.25</v>
+      </c>
+      <c r="G823" t="n">
+        <v>373.09</v>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:54:09+00:00</t>
+        </is>
+      </c>
+      <c r="B824" t="n">
+        <v>380.13</v>
+      </c>
+      <c r="C824" t="n">
+        <v>389.95</v>
+      </c>
+      <c r="D824" t="n">
+        <v>392.19</v>
+      </c>
+      <c r="E824" t="n">
+        <v>390.96</v>
+      </c>
+      <c r="F824" t="n">
+        <v>388.33</v>
+      </c>
+      <c r="G824" t="n">
+        <v>373.26</v>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:13+00:00</t>
+        </is>
+      </c>
+      <c r="B825" t="n">
+        <v>379.13</v>
+      </c>
+      <c r="C825" t="n">
+        <v>390.29</v>
+      </c>
+      <c r="D825" t="n">
+        <v>392.7</v>
+      </c>
+      <c r="E825" t="n">
+        <v>391.52</v>
+      </c>
+      <c r="F825" t="n">
+        <v>388.71</v>
+      </c>
+      <c r="G825" t="n">
+        <v>374.13</v>
+      </c>
+      <c r="H825" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25084,7 +25204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B832"/>
+  <dimension ref="A1:B836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33407,6 +33527,46 @@
       </c>
       <c r="B832" t="n">
         <v>0.57</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B833" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B834" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B835" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B836" t="n">
+        <v>-0.5</v>
       </c>
     </row>
   </sheetData>
@@ -33575,28 +33735,28 @@
         <v>0.0479</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2980296431200929</v>
+        <v>-0.2946644452204396</v>
       </c>
       <c r="J2" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="K2" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1240893570689021</v>
+        <v>0.1226983564690122</v>
       </c>
       <c r="M2" t="n">
-        <v>4.530637300671871</v>
+        <v>4.523945350903762</v>
       </c>
       <c r="N2" t="n">
-        <v>34.42685936197478</v>
+        <v>34.31705885057693</v>
       </c>
       <c r="O2" t="n">
-        <v>5.867440614269119</v>
+        <v>5.858076378008136</v>
       </c>
       <c r="P2" t="n">
-        <v>383.9428392955392</v>
+        <v>383.9080952367079</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33653,28 +33813,28 @@
         <v>0.0776</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.251136474213718</v>
+        <v>-0.2516852071006792</v>
       </c>
       <c r="J3" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="K3" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1475356160831155</v>
+        <v>0.1495340037272012</v>
       </c>
       <c r="M3" t="n">
-        <v>3.503806894690102</v>
+        <v>3.489346498848151</v>
       </c>
       <c r="N3" t="n">
-        <v>20.01023389650112</v>
+        <v>19.91483731771781</v>
       </c>
       <c r="O3" t="n">
-        <v>4.473279993081264</v>
+        <v>4.462604320093572</v>
       </c>
       <c r="P3" t="n">
-        <v>397.5046801723875</v>
+        <v>397.5103452092728</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33731,28 +33891,28 @@
         <v>0.0718</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.182262151885162</v>
+        <v>-0.1819049515723765</v>
       </c>
       <c r="J4" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="K4" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1327549813408605</v>
+        <v>0.1336123384608802</v>
       </c>
       <c r="M4" t="n">
-        <v>2.880193772074448</v>
+        <v>2.868813481624911</v>
       </c>
       <c r="N4" t="n">
-        <v>11.91618359608727</v>
+        <v>11.86039424220127</v>
       </c>
       <c r="O4" t="n">
-        <v>3.451982560223512</v>
+        <v>3.443892309901874</v>
       </c>
       <c r="P4" t="n">
-        <v>396.4666841274685</v>
+        <v>396.4629930995787</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33809,28 +33969,28 @@
         <v>0.0693</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0671770047040945</v>
+        <v>-0.06591269352665598</v>
       </c>
       <c r="J5" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="K5" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="L5" t="n">
-        <v>0.025367816189107</v>
+        <v>0.02470132599561747</v>
       </c>
       <c r="M5" t="n">
-        <v>2.492707182237735</v>
+        <v>2.487014676632754</v>
       </c>
       <c r="N5" t="n">
-        <v>9.520333195298015</v>
+        <v>9.481998340104797</v>
       </c>
       <c r="O5" t="n">
-        <v>3.085503718244075</v>
+        <v>3.07928536191513</v>
       </c>
       <c r="P5" t="n">
-        <v>391.648639246808</v>
+        <v>391.6355854886943</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33887,28 +34047,28 @@
         <v>0.0736</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02464437028592497</v>
+        <v>-0.02643990124405236</v>
       </c>
       <c r="J6" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="K6" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001702320994652062</v>
+        <v>0.001979987218658441</v>
       </c>
       <c r="M6" t="n">
-        <v>3.660233621667925</v>
+        <v>3.651160391899137</v>
       </c>
       <c r="N6" t="n">
-        <v>19.55722661487264</v>
+        <v>19.47784521033068</v>
       </c>
       <c r="O6" t="n">
-        <v>4.422355324357444</v>
+        <v>4.413371184291061</v>
       </c>
       <c r="P6" t="n">
-        <v>390.8385845733497</v>
+        <v>390.8571204057146</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33965,28 +34125,28 @@
         <v>0.0537</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0424219951817704</v>
+        <v>-0.04351737470051297</v>
       </c>
       <c r="J7" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="K7" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004485234698441976</v>
+        <v>0.004771688765265014</v>
       </c>
       <c r="M7" t="n">
-        <v>3.822883811487078</v>
+        <v>3.809167151486961</v>
       </c>
       <c r="N7" t="n">
-        <v>21.93299421550751</v>
+        <v>21.83335003856936</v>
       </c>
       <c r="O7" t="n">
-        <v>4.683267472129636</v>
+        <v>4.672617043859828</v>
       </c>
       <c r="P7" t="n">
-        <v>375.5599930181323</v>
+        <v>375.5712988179779</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34024,7 +34184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H821"/>
+  <dimension ref="A1:H825"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68509,6 +68669,174 @@
         </is>
       </c>
     </row>
+    <row r="822">
+      <c r="A822" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:03+00:00</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>-39.30030990263516,176.97764160637402</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>-39.30080075652058,176.9770561068439</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>-39.301299766695514,176.9765118304019</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>-39.30183785842138,176.975969560164</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>-39.30235590284666,176.97543353379353</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>-39.30289896331315,176.97490064465876</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-07 22:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>-39.300323620175455,176.97765641849654</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>-39.30080327994465,176.9770594099315</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>-39.30130327291623,176.97651771003345</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>-39.3018381700434,176.9759701275864</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>-39.302355859029674,176.97543343264124</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>-39.30289972437797,176.97490287073074</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:54:09+00:00</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>-39.300323551243096,176.97765634406375</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>-39.30079886395245,176.9770536295283</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>-39.30130519038054,176.97652092545715</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>-39.30183775454737,176.9759693710232</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>-39.30235620956549,176.97543424185946</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>-39.30290034047805,176.97490467278905</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:13+00:00</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>-39.300316658007056,176.9776489007854</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>-39.30080100886299,176.97705643715264</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>-39.301307984399806,176.9765256107892</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>-39.30184066301943,176.97597466696584</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>-39.30235787461046,176.975438085646</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>-39.30290349346029,176.97491389508792</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0290/nzd0290.xlsx
+++ b/data/nzd0290/nzd0290.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H825"/>
+  <dimension ref="A1:H831"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25188,6 +25188,186 @@
         <v>374.13</v>
       </c>
       <c r="H825" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B826" t="n">
+        <v>378.15</v>
+      </c>
+      <c r="C826" t="n">
+        <v>390.12</v>
+      </c>
+      <c r="D826" t="n">
+        <v>392.7</v>
+      </c>
+      <c r="E826" t="n">
+        <v>391.49</v>
+      </c>
+      <c r="F826" t="n">
+        <v>388.24</v>
+      </c>
+      <c r="G826" t="n">
+        <v>374.27</v>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-23 21:59:59+00:00</t>
+        </is>
+      </c>
+      <c r="B827" t="n">
+        <v>379.02</v>
+      </c>
+      <c r="C827" t="n">
+        <v>390.66</v>
+      </c>
+      <c r="D827" t="n">
+        <v>392.85</v>
+      </c>
+      <c r="E827" t="n">
+        <v>391.9</v>
+      </c>
+      <c r="F827" t="n">
+        <v>388.61</v>
+      </c>
+      <c r="G827" t="n">
+        <v>374.62</v>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B828" t="n">
+        <v>378.06</v>
+      </c>
+      <c r="C828" t="n">
+        <v>389.58</v>
+      </c>
+      <c r="D828" t="n">
+        <v>392.61</v>
+      </c>
+      <c r="E828" t="n">
+        <v>392.28</v>
+      </c>
+      <c r="F828" t="n">
+        <v>388.63</v>
+      </c>
+      <c r="G828" t="n">
+        <v>374.78</v>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:59:50+00:00</t>
+        </is>
+      </c>
+      <c r="B829" t="n">
+        <v>378.18</v>
+      </c>
+      <c r="C829" t="n">
+        <v>389.25</v>
+      </c>
+      <c r="D829" t="n">
+        <v>392.88</v>
+      </c>
+      <c r="E829" t="n">
+        <v>392.74</v>
+      </c>
+      <c r="F829" t="n">
+        <v>388.72</v>
+      </c>
+      <c r="G829" t="n">
+        <v>375.83</v>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B830" t="n">
+        <v>376.63</v>
+      </c>
+      <c r="C830" t="n">
+        <v>388.55</v>
+      </c>
+      <c r="D830" t="n">
+        <v>392.92</v>
+      </c>
+      <c r="E830" t="n">
+        <v>392.92</v>
+      </c>
+      <c r="F830" t="n">
+        <v>388.77</v>
+      </c>
+      <c r="G830" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B831" t="n">
+        <v>376.01</v>
+      </c>
+      <c r="C831" t="n">
+        <v>388.13</v>
+      </c>
+      <c r="D831" t="n">
+        <v>392.83</v>
+      </c>
+      <c r="E831" t="n">
+        <v>392.78</v>
+      </c>
+      <c r="F831" t="n">
+        <v>388.93</v>
+      </c>
+      <c r="G831" t="n">
+        <v>376.25</v>
+      </c>
+      <c r="H831" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25204,7 +25384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B836"/>
+  <dimension ref="A1:B842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33567,6 +33747,66 @@
       </c>
       <c r="B836" t="n">
         <v>-0.5</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B837" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B838" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B839" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B840" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B841" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B842" t="n">
+        <v>-0.17</v>
       </c>
     </row>
   </sheetData>
@@ -33735,28 +33975,28 @@
         <v>0.0479</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2946644452204396</v>
+        <v>-0.2922795955958589</v>
       </c>
       <c r="J2" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="K2" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1226983564690122</v>
+        <v>0.1227033685885497</v>
       </c>
       <c r="M2" t="n">
-        <v>4.523945350903762</v>
+        <v>4.502288464020117</v>
       </c>
       <c r="N2" t="n">
-        <v>34.31705885057693</v>
+        <v>34.09497094654382</v>
       </c>
       <c r="O2" t="n">
-        <v>5.858076378008136</v>
+        <v>5.83908990738658</v>
       </c>
       <c r="P2" t="n">
-        <v>383.9080952367079</v>
+        <v>383.883417593761</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33813,28 +34053,28 @@
         <v>0.0776</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2516852071006792</v>
+        <v>-0.2537837857835614</v>
       </c>
       <c r="J3" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="K3" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1495340037272012</v>
+        <v>0.1537379474904116</v>
       </c>
       <c r="M3" t="n">
-        <v>3.489346498848151</v>
+        <v>3.473713622436507</v>
       </c>
       <c r="N3" t="n">
-        <v>19.91483731771781</v>
+        <v>19.79041423602485</v>
       </c>
       <c r="O3" t="n">
-        <v>4.462604320093572</v>
+        <v>4.448641841733817</v>
       </c>
       <c r="P3" t="n">
-        <v>397.5103452092728</v>
+        <v>397.5320978262608</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33891,28 +34131,28 @@
         <v>0.0718</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1819049515723765</v>
+        <v>-0.1801616988608994</v>
       </c>
       <c r="J4" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="K4" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1336123384608802</v>
+        <v>0.1332606294628819</v>
       </c>
       <c r="M4" t="n">
-        <v>2.868813481624911</v>
+        <v>2.85561637025629</v>
       </c>
       <c r="N4" t="n">
-        <v>11.86039424220127</v>
+        <v>11.78460292447668</v>
       </c>
       <c r="O4" t="n">
-        <v>3.443892309901874</v>
+        <v>3.432870944920109</v>
       </c>
       <c r="P4" t="n">
-        <v>396.4629930995787</v>
+        <v>396.4449380690421</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33969,28 +34209,28 @@
         <v>0.0693</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06591269352665598</v>
+        <v>-0.06226199325605369</v>
       </c>
       <c r="J5" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="K5" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02470132599561747</v>
+        <v>0.02236657661667107</v>
       </c>
       <c r="M5" t="n">
-        <v>2.487014676632754</v>
+        <v>2.487295080522909</v>
       </c>
       <c r="N5" t="n">
-        <v>9.481998340104797</v>
+        <v>9.458579468851129</v>
       </c>
       <c r="O5" t="n">
-        <v>3.07928536191513</v>
+        <v>3.075480363918965</v>
       </c>
       <c r="P5" t="n">
-        <v>391.6355854886943</v>
+        <v>391.597766311543</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34047,28 +34287,28 @@
         <v>0.0736</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02643990124405236</v>
+        <v>-0.02865414410544022</v>
       </c>
       <c r="J6" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="K6" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001979987218658441</v>
+        <v>0.002362632503127737</v>
       </c>
       <c r="M6" t="n">
-        <v>3.651160391899137</v>
+        <v>3.635343416981442</v>
       </c>
       <c r="N6" t="n">
-        <v>19.47784521033068</v>
+        <v>19.35328836776126</v>
       </c>
       <c r="O6" t="n">
-        <v>4.413371184291061</v>
+        <v>4.399237248405825</v>
       </c>
       <c r="P6" t="n">
-        <v>390.8571204057146</v>
+        <v>390.8800471102371</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34125,28 +34365,28 @@
         <v>0.0537</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04351737470051297</v>
+        <v>-0.04208309567826247</v>
       </c>
       <c r="J7" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="K7" t="n">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004771688765265014</v>
+        <v>0.004537672706006468</v>
       </c>
       <c r="M7" t="n">
-        <v>3.809167151486961</v>
+        <v>3.789488795639638</v>
       </c>
       <c r="N7" t="n">
-        <v>21.83335003856936</v>
+        <v>21.68754399873617</v>
       </c>
       <c r="O7" t="n">
-        <v>4.672617043859828</v>
+        <v>4.65698872649872</v>
       </c>
       <c r="P7" t="n">
-        <v>375.5712988179779</v>
+        <v>375.5564258772104</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34184,7 +34424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H825"/>
+  <dimension ref="A1:H831"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68837,6 +69077,258 @@
         </is>
       </c>
     </row>
+    <row r="826">
+      <c r="A826" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:52+00:00</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>-39.30030990263516,176.97764160637402</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>-39.300799936407714,176.97705503334046</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>-39.301307984399806,176.9765256107892</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>-39.30184050720844,176.97597438325462</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>-39.30235581521271,176.97543333148897</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>-39.302904000836676,176.9749153791361</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-23 21:59:59+00:00</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>-39.300315899751055,176.97764808202484</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>-39.30080334303025,176.97705949250872</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>-39.30130880617013,176.9765269888281</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>-39.30184263662532,176.97597826064145</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>-39.302357436440744,176.97543707412322</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>-39.302905269277545,176.9749190892566</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>-39.30030928224385,176.97764093647916</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>-39.30079652978501,176.9770505741726</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>-39.30130749133759,176.97652478396586</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>-39.30184461023108,176.97598185431727</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>-39.30235752407469,176.97543727642778</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>-39.30290584913618,176.97492078531172</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 21:59:50+00:00</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>-39.30031010943228,176.9776418296723</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>-39.300794447959916,176.97704784912582</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>-39.30130897052418,176.97652726443587</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>-39.301846999332625,176.97598620455665</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>-39.30235791842744,176.9754381867983</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>-39.30290965445784,176.97493191567415</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>-39.30029942491447,176.9776302925959</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>-39.300790031967054,176.97704206872407</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>-39.30130918966294,176.97652763191292</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>-39.30184793419841,176.97598790682432</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>-39.302358137512286,176.97543869255972</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>-39.30291222757947,176.97493944191987</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>-39.30029515110698,176.97762567776635</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>-39.30078738237118,176.97703860048335</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>-39.301308696600756,176.97652680508958</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>-39.301847207080584,176.97598658283835</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>-39.30235883858381,176.97544031099622</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>-39.30291117658619,176.97493636781945</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0290/nzd0290.xlsx
+++ b/data/nzd0290/nzd0290.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H831"/>
+  <dimension ref="A1:H836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25368,6 +25368,156 @@
         <v>376.25</v>
       </c>
       <c r="H831" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 21:59:55+00:00</t>
+        </is>
+      </c>
+      <c r="B832" t="n">
+        <v>374.6</v>
+      </c>
+      <c r="C832" t="n">
+        <v>387.71</v>
+      </c>
+      <c r="D832" t="n">
+        <v>392.52</v>
+      </c>
+      <c r="E832" t="n">
+        <v>392.55</v>
+      </c>
+      <c r="F832" t="n">
+        <v>388.29</v>
+      </c>
+      <c r="G832" t="n">
+        <v>375.96</v>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B833" t="n">
+        <v>373.92</v>
+      </c>
+      <c r="C833" t="n">
+        <v>387.76</v>
+      </c>
+      <c r="D833" t="n">
+        <v>392.24</v>
+      </c>
+      <c r="E833" t="n">
+        <v>392.57</v>
+      </c>
+      <c r="F833" t="n">
+        <v>388.2</v>
+      </c>
+      <c r="G833" t="n">
+        <v>375.94</v>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:35+00:00</t>
+        </is>
+      </c>
+      <c r="B834" t="n">
+        <v>372.17</v>
+      </c>
+      <c r="C834" t="n">
+        <v>387.24</v>
+      </c>
+      <c r="D834" t="n">
+        <v>391.78</v>
+      </c>
+      <c r="E834" t="n">
+        <v>392.49</v>
+      </c>
+      <c r="F834" t="n">
+        <v>388.52</v>
+      </c>
+      <c r="G834" t="n">
+        <v>376.15</v>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:10+00:00</t>
+        </is>
+      </c>
+      <c r="B835" t="n">
+        <v>371.17</v>
+      </c>
+      <c r="C835" t="n">
+        <v>386.71</v>
+      </c>
+      <c r="D835" t="n">
+        <v>391.18</v>
+      </c>
+      <c r="E835" t="n">
+        <v>392.09</v>
+      </c>
+      <c r="F835" t="n">
+        <v>388.09</v>
+      </c>
+      <c r="G835" t="n">
+        <v>376.13</v>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B836" t="n">
+        <v>370.69</v>
+      </c>
+      <c r="C836" t="n">
+        <v>386.78</v>
+      </c>
+      <c r="D836" t="n">
+        <v>391.31</v>
+      </c>
+      <c r="E836" t="n">
+        <v>391.65</v>
+      </c>
+      <c r="F836" t="n">
+        <v>387.83</v>
+      </c>
+      <c r="G836" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="H836" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25384,7 +25534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B842"/>
+  <dimension ref="A1:B847"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33807,6 +33957,56 @@
       </c>
       <c r="B842" t="n">
         <v>-0.17</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B843" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B844" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B845" t="n">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B846" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B847" t="n">
+        <v>-0.59</v>
       </c>
     </row>
   </sheetData>
@@ -33975,28 +34175,28 @@
         <v>0.0479</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2922795955958589</v>
+        <v>-0.2966057465975193</v>
       </c>
       <c r="J2" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="K2" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1227033685885497</v>
+        <v>0.1271701139553988</v>
       </c>
       <c r="M2" t="n">
-        <v>4.502288464020117</v>
+        <v>4.497637393905887</v>
       </c>
       <c r="N2" t="n">
-        <v>34.09497094654382</v>
+        <v>33.97878727584401</v>
       </c>
       <c r="O2" t="n">
-        <v>5.83908990738658</v>
+        <v>5.829132634950418</v>
       </c>
       <c r="P2" t="n">
-        <v>383.883417593761</v>
+        <v>383.9284319525247</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34053,28 +34253,28 @@
         <v>0.0776</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2537837857835614</v>
+        <v>-0.2580412244648453</v>
       </c>
       <c r="J3" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="K3" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1537379474904116</v>
+        <v>0.159500576877689</v>
       </c>
       <c r="M3" t="n">
-        <v>3.473713622436507</v>
+        <v>3.472282359766937</v>
       </c>
       <c r="N3" t="n">
-        <v>19.79041423602485</v>
+        <v>19.74501892727606</v>
       </c>
       <c r="O3" t="n">
-        <v>4.448641841733817</v>
+        <v>4.443536758852802</v>
       </c>
       <c r="P3" t="n">
-        <v>397.5320978262608</v>
+        <v>397.5763831903972</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34131,28 +34331,28 @@
         <v>0.0718</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1801616988608994</v>
+        <v>-0.1799440188113258</v>
       </c>
       <c r="J4" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="K4" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1332606294628819</v>
+        <v>0.1345942934034855</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85561637025629</v>
+        <v>2.841270547840089</v>
       </c>
       <c r="N4" t="n">
-        <v>11.78460292447668</v>
+        <v>11.71580524912178</v>
       </c>
       <c r="O4" t="n">
-        <v>3.432870944920109</v>
+        <v>3.422835848988639</v>
       </c>
       <c r="P4" t="n">
-        <v>396.4449380690421</v>
+        <v>396.442680579254</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34209,28 +34409,28 @@
         <v>0.0693</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06226199325605369</v>
+        <v>-0.05942128841944686</v>
       </c>
       <c r="J5" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="K5" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02236657661667107</v>
+        <v>0.02062556168961238</v>
       </c>
       <c r="M5" t="n">
-        <v>2.487295080522909</v>
+        <v>2.486644608559642</v>
       </c>
       <c r="N5" t="n">
-        <v>9.458579468851129</v>
+        <v>9.434769917420153</v>
       </c>
       <c r="O5" t="n">
-        <v>3.075480363918965</v>
+        <v>3.071607057782644</v>
       </c>
       <c r="P5" t="n">
-        <v>391.597766311543</v>
+        <v>391.5682260703404</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34287,28 +34487,28 @@
         <v>0.0736</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.02865414410544022</v>
+        <v>-0.03099582242820752</v>
       </c>
       <c r="J6" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="K6" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002362632503127737</v>
+        <v>0.002799294003983266</v>
       </c>
       <c r="M6" t="n">
-        <v>3.635343416981442</v>
+        <v>3.624584095022104</v>
       </c>
       <c r="N6" t="n">
-        <v>19.35328836776126</v>
+        <v>19.25948174683566</v>
       </c>
       <c r="O6" t="n">
-        <v>4.399237248405825</v>
+        <v>4.388562606006169</v>
       </c>
       <c r="P6" t="n">
-        <v>390.8800471102371</v>
+        <v>390.9044040050559</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34365,28 +34565,28 @@
         <v>0.0537</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04208309567826247</v>
+        <v>-0.04026794688226022</v>
       </c>
       <c r="J7" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="K7" t="n">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004537672706006468</v>
+        <v>0.004212272683721152</v>
       </c>
       <c r="M7" t="n">
-        <v>3.789488795639638</v>
+        <v>3.776259133173929</v>
       </c>
       <c r="N7" t="n">
-        <v>21.68754399873617</v>
+        <v>21.57115853268878</v>
       </c>
       <c r="O7" t="n">
-        <v>4.65698872649872</v>
+        <v>4.64447613113565</v>
       </c>
       <c r="P7" t="n">
-        <v>375.5564258772104</v>
+        <v>375.5375491734264</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34424,7 +34624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H831"/>
+  <dimension ref="A1:H836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69329,6 +69529,216 @@
         </is>
       </c>
     </row>
+    <row r="832">
+      <c r="A832" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 21:59:55+00:00</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>-39.30028543164073,176.97761518275288</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>-39.300784732775185,176.9770351322429</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>-39.30130699827538,176.97652395714255</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>-39.301846012529836,176.97598440771858</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>-39.302356034297574,176.97543383725036</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>-39.30291012559284,176.97493329371912</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>-39.30028074423819,176.977610121329</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>-39.30078504820328,176.97703554512867</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>-39.30130546430401,176.97652138480342</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>-39.30184611640381,176.97598459685943</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>-39.302355639944786,176.97543292687988</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>-39.30291005311052,176.97493308171218</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:35+00:00</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>-39.30026868106866,176.9775970956089</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>-39.30078176775097,176.977031251117</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>-39.301302944208054,176.97651715881798</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>-39.301845700907904,176.97598384029607</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>-39.30235704208798,176.9754361637527</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>-39.3029108141747,176.97493530778485</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:10+00:00</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>-39.300261787828155,176.97758965234232</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>-39.30077842421283,176.97702687452863</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>-39.301299657126116,176.97651164666345</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>-39.30184362342821,176.97598005747932</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>-39.302355157958054,176.97543181420488</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>-39.3029107416924,176.97493509577794</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-27 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>-39.30025847907252,176.97758607957488</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>-39.300778865812205,176.97702745256856</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>-39.30130036932722,176.97651284096355</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>-39.301841338200404,176.97597589638116</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>-39.302354018716606,176.97542918424583</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>-39.30290824105279,176.9749277815394</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0290/nzd0290.xlsx
+++ b/data/nzd0290/nzd0290.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H836"/>
+  <dimension ref="A1:H840"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25518,6 +25518,126 @@
         <v>375.44</v>
       </c>
       <c r="H836" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 21:59:29+00:00</t>
+        </is>
+      </c>
+      <c r="B837" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="C837" t="n">
+        <v>386.7</v>
+      </c>
+      <c r="D837" t="n">
+        <v>391.11</v>
+      </c>
+      <c r="E837" t="n">
+        <v>391.43</v>
+      </c>
+      <c r="F837" t="n">
+        <v>387.37</v>
+      </c>
+      <c r="G837" t="n">
+        <v>375.16</v>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:59:21+00:00</t>
+        </is>
+      </c>
+      <c r="B838" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="C838" t="n">
+        <v>387.37</v>
+      </c>
+      <c r="D838" t="n">
+        <v>391.51</v>
+      </c>
+      <c r="E838" t="n">
+        <v>391.38</v>
+      </c>
+      <c r="F838" t="n">
+        <v>386.94</v>
+      </c>
+      <c r="G838" t="n">
+        <v>374.92</v>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B839" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="C839" t="n">
+        <v>387.53</v>
+      </c>
+      <c r="D839" t="n">
+        <v>391.57</v>
+      </c>
+      <c r="E839" t="n">
+        <v>391.15</v>
+      </c>
+      <c r="F839" t="n">
+        <v>386.46</v>
+      </c>
+      <c r="G839" t="n">
+        <v>374.35</v>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B840" t="n">
+        <v>362.14</v>
+      </c>
+      <c r="C840" t="n">
+        <v>387.77</v>
+      </c>
+      <c r="D840" t="n">
+        <v>391.53</v>
+      </c>
+      <c r="E840" t="n">
+        <v>391.21</v>
+      </c>
+      <c r="F840" t="n">
+        <v>386.24</v>
+      </c>
+      <c r="G840" t="n">
+        <v>374.21</v>
+      </c>
+      <c r="H840" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25534,7 +25654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B847"/>
+  <dimension ref="A1:B851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34007,6 +34127,46 @@
       </c>
       <c r="B847" t="n">
         <v>-0.59</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-06-03 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B848" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B849" t="n">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B850" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-06-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B851" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -34175,28 +34335,28 @@
         <v>0.0479</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2966057465975193</v>
+        <v>-0.3048443458014085</v>
       </c>
       <c r="J2" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="K2" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1271701139553988</v>
+        <v>0.1333458380574168</v>
       </c>
       <c r="M2" t="n">
-        <v>4.497637393905887</v>
+        <v>4.51911380819242</v>
       </c>
       <c r="N2" t="n">
-        <v>33.97878727584401</v>
+        <v>34.20537111511241</v>
       </c>
       <c r="O2" t="n">
-        <v>5.829132634950418</v>
+        <v>5.848535809509284</v>
       </c>
       <c r="P2" t="n">
-        <v>383.9284319525247</v>
+        <v>384.0144242185887</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34253,28 +34413,28 @@
         <v>0.0776</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2580412244648453</v>
+        <v>-0.2612312826309116</v>
       </c>
       <c r="J3" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="K3" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="L3" t="n">
-        <v>0.159500576877689</v>
+        <v>0.1639843879929379</v>
       </c>
       <c r="M3" t="n">
-        <v>3.472282359766937</v>
+        <v>3.470328723894063</v>
       </c>
       <c r="N3" t="n">
-        <v>19.74501892727606</v>
+        <v>19.70307027720566</v>
       </c>
       <c r="O3" t="n">
-        <v>4.443536758852802</v>
+        <v>4.438814062022159</v>
       </c>
       <c r="P3" t="n">
-        <v>397.5763831903972</v>
+        <v>397.609670662504</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34331,28 +34491,28 @@
         <v>0.0718</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1799440188113258</v>
+        <v>-0.1801236583166625</v>
       </c>
       <c r="J4" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="K4" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1345942934034855</v>
+        <v>0.1361296218661542</v>
       </c>
       <c r="M4" t="n">
-        <v>2.841270547840089</v>
+        <v>2.828705667364862</v>
       </c>
       <c r="N4" t="n">
-        <v>11.71580524912178</v>
+        <v>11.66028373926422</v>
       </c>
       <c r="O4" t="n">
-        <v>3.422835848988639</v>
+        <v>3.414715762587601</v>
       </c>
       <c r="P4" t="n">
-        <v>396.442680579254</v>
+        <v>396.4445541820428</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34409,28 +34569,28 @@
         <v>0.0693</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05942128841944686</v>
+        <v>-0.05815002526336027</v>
       </c>
       <c r="J5" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="K5" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02062556168961238</v>
+        <v>0.01996984133119695</v>
       </c>
       <c r="M5" t="n">
-        <v>2.486644608559642</v>
+        <v>2.48109346973505</v>
       </c>
       <c r="N5" t="n">
-        <v>9.434769917420153</v>
+        <v>9.398018558238283</v>
       </c>
       <c r="O5" t="n">
-        <v>3.071607057782644</v>
+        <v>3.065618788799136</v>
       </c>
       <c r="P5" t="n">
-        <v>391.5682260703404</v>
+        <v>391.5549602900738</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34487,28 +34647,28 @@
         <v>0.0736</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03099582242820752</v>
+        <v>-0.03419707205526894</v>
       </c>
       <c r="J6" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="K6" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002799294003983266</v>
+        <v>0.003433961679050856</v>
       </c>
       <c r="M6" t="n">
-        <v>3.624584095022104</v>
+        <v>3.622213737993454</v>
       </c>
       <c r="N6" t="n">
-        <v>19.25948174683566</v>
+        <v>19.22029910886431</v>
       </c>
       <c r="O6" t="n">
-        <v>4.388562606006169</v>
+        <v>4.384096156434564</v>
       </c>
       <c r="P6" t="n">
-        <v>390.9044040050559</v>
+        <v>390.9378134392362</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34565,28 +34725,28 @@
         <v>0.0537</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04026794688226022</v>
+        <v>-0.04007163008424887</v>
       </c>
       <c r="J7" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="K7" t="n">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004212272683721152</v>
+        <v>0.004217869776222072</v>
       </c>
       <c r="M7" t="n">
-        <v>3.776259133173929</v>
+        <v>3.760123191050841</v>
       </c>
       <c r="N7" t="n">
-        <v>21.57115853268878</v>
+        <v>21.46924820869836</v>
       </c>
       <c r="O7" t="n">
-        <v>4.64447613113565</v>
+        <v>4.633492010211992</v>
       </c>
       <c r="P7" t="n">
-        <v>375.5375491734264</v>
+        <v>375.5355027634163</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34624,7 +34784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H836"/>
+  <dimension ref="A1:H840"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69739,6 +69899,174 @@
         </is>
       </c>
     </row>
+    <row r="837">
+      <c r="A837" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 21:59:29+00:00</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>-39.30025503245192,176.97758235794248</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>-39.3007783611272,176.9770267919515</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>-39.301299273633205,176.9765110035788</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>-39.301840195586436,176.97597381583216</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>-39.302352003135425,176.97542453124154</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>-39.302907226300334,176.97492481344275</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:59:21+00:00</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>-39.30024469258931,176.97757119304757</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>-39.30078258786406,176.97703232461987</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>-39.30130146502121,176.97651467834837</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>-39.301839935901434,176.97597334298015</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>-39.30235011900503,176.97542018169432</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>-39.30290635651246,176.97492226935998</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:22+00:00</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>-39.30024469258931,176.97757119304757</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>-39.30078359723401,176.97703364585422</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>-39.3013017937294,176.97651522956383</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>-39.30183874135043,176.97597116786082</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>-39.302348015789484,176.975415326386</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>-39.30290429076603,176.97491622716362</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>-39.300199541841195,176.97752243971212</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>-39.300785111288896,176.97703562770582</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>-39.30130157459062,176.97651486208684</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>-39.30183905297243,176.97597173528325</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>-39.302347051815616,176.97541310103648</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>-39.30290378338965,176.97491474311542</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
